--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,32 +903,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127131873</v>
+        <v>127131856</v>
       </c>
       <c r="B4" t="n">
-        <v>58290</v>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102125</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1012,32 +1012,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127131856</v>
+        <v>127131884</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102977</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127131884</v>
+        <v>127131819</v>
       </c>
       <c r="B6" t="n">
-        <v>57815</v>
+        <v>57654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,16 +1132,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1227,115 +1227,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>127131819</v>
-      </c>
-      <c r="B7" t="n">
-        <v>57654</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Deromeskogen, Hl</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>322797</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6373105</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Halland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Kungsbacka</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Halland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Vallda</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Carolos Borg</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Carolos Borg</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1228,6 +1228,111 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127131873</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58290</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Deromeskogen, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>322797</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6373105</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vallda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Carolos Borg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Carolos Borg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>127131832</v>
       </c>
       <c r="B3" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127131856</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57655</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>127131884</v>
       </c>
       <c r="B5" t="n">
-        <v>57815</v>
+        <v>57819</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127131819</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>127131873</v>
       </c>
       <c r="B7" t="n">
-        <v>58290</v>
+        <v>58294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1333,6 +1333,572 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127704348</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58138</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100058</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre flugsnappare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ficedula parva</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1794)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Deromeskogen, Hl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>322797</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6373105</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vallda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Carolos Borg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Carolos Borg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127704592</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58096</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Deromeskogen, Hl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>322797</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6373105</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vallda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Carolos Borg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Carolos Borg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127704700</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57821</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Deromeskogen, Hl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>322797</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6373105</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vallda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Carolos Borg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Carolos Borg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127704255</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58091</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Deromeskogen, Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>322797</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6373105</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vallda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Carolos Borg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Carolos Borg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127705066</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57534</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100096</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pandion haliaetus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Deromeskogen, Hl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>322797</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6373105</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vallda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Carolos Borg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Carolos Borg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>127131832</v>
       </c>
       <c r="B3" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127131856</v>
       </c>
       <c r="B4" t="n">
-        <v>57655</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>127131884</v>
       </c>
       <c r="B5" t="n">
-        <v>57819</v>
+        <v>57821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127131819</v>
       </c>
       <c r="B6" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>127131873</v>
       </c>
       <c r="B7" t="n">
-        <v>58294</v>
+        <v>58296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>127704348</v>
       </c>
       <c r="B8" t="n">
-        <v>58138</v>
+        <v>58140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>127704592</v>
       </c>
       <c r="B9" t="n">
-        <v>58096</v>
+        <v>58098</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127704700</v>
       </c>
       <c r="B10" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>127704255</v>
       </c>
       <c r="B11" t="n">
-        <v>58091</v>
+        <v>58093</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>127705066</v>
       </c>
       <c r="B12" t="n">
-        <v>57534</v>
+        <v>57536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1899,6 +1899,351 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127756127</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56538</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Oskarsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>322874</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6373103</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vallda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt vattenfladdermus. Observationen bygger på flera registreringar, artbestämningen säker.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gabriel  Ulvros</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gabriel  Ulvros</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127756180</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56531</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Oskarsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>322874</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6373103</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vallda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt nordfladdermus. Observationen bygger på flera registreringar, artbestämningen säker.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gabriel  Ulvros</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gabriel  Ulvros</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127756227</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56550</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Oskarsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>322874</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6373103</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vallda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt dvärgpipistrell. Observationen bygger på flera registreringar, artbestämningen säker.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gabriel  Ulvros</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gabriel  Ulvros</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -1335,32 +1335,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127704348</v>
+        <v>127704182</v>
       </c>
       <c r="B8" t="n">
-        <v>58140</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100058</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre flugsnappare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ficedula parva</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bechstein, 1794)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1449,60 +1449,61 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127704592</v>
+        <v>127756127</v>
       </c>
       <c r="B9" t="n">
-        <v>58098</v>
+        <v>56538</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102999</v>
+        <v>205992</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Deromeskogen, Hl</t>
+          <t>Oskarsberg, Hl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>322797</v>
+        <v>322874</v>
       </c>
       <c r="R9" t="n">
-        <v>6373105</v>
+        <v>6373103</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,17 +1527,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33</t>
+          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt vattenfladdermus. Observationen bygger på flera registreringar, artbestämningen säker.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,22 +1552,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Carolos Borg</t>
+          <t>Gabriel  Ulvros</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carolos Borg</t>
+          <t>Gabriel  Ulvros</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127704700</v>
+        <v>127756180</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>56531</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,49 +1575,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>205998</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Deromeskogen, Hl</t>
+          <t>Oskarsberg, Hl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>322797</v>
+        <v>322874</v>
       </c>
       <c r="R10" t="n">
-        <v>6373105</v>
+        <v>6373103</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,17 +1642,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33</t>
+          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt nordfladdermus. Observationen bygger på flera registreringar, artbestämningen säker.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,72 +1667,73 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Carolos Borg</t>
+          <t>Gabriel  Ulvros</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carolos Borg</t>
+          <t>Gabriel  Ulvros</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127704255</v>
+        <v>127756227</v>
       </c>
       <c r="B11" t="n">
-        <v>58093</v>
+        <v>56550</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103001</v>
+        <v>205995</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Deromeskogen, Hl</t>
+          <t>Oskarsberg, Hl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>322797</v>
+        <v>322874</v>
       </c>
       <c r="R11" t="n">
-        <v>6373105</v>
+        <v>6373103</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1764,7 +1767,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33</t>
+          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt dvärgpipistrell. Observationen bygger på flera registreringar, artbestämningen säker.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,22 +1782,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Carolos Borg</t>
+          <t>Gabriel  Ulvros</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carolos Borg</t>
+          <t>Gabriel  Ulvros</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127705066</v>
+        <v>127704348</v>
       </c>
       <c r="B12" t="n">
-        <v>57536</v>
+        <v>58140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,27 +1805,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100096</v>
+        <v>100058</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Mindre flugsnappare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Ficedula parva</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1794)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1864,17 +1871,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33</t>
+          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33 Analysprogram: Chirpity</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,61 +1908,60 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127756127</v>
+        <v>127704592</v>
       </c>
       <c r="B13" t="n">
-        <v>56538</v>
+        <v>58098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205992</v>
+        <v>102999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Oskarsberg, Hl</t>
+          <t>Deromeskogen, Hl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>322874</v>
+        <v>322797</v>
       </c>
       <c r="R13" t="n">
-        <v>6373103</v>
+        <v>6373105</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1979,17 +1985,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt vattenfladdermus. Observationen bygger på flera registreringar, artbestämningen säker.</t>
+          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33 Analysprogram: Chirpity</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,22 +2010,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Gabriel  Ulvros</t>
+          <t>Carolos Borg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Gabriel  Ulvros</t>
+          <t>Carolos Borg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127756180</v>
+        <v>127704255</v>
       </c>
       <c r="B14" t="n">
-        <v>56531</v>
+        <v>58093</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,50 +2033,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>103001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Oskarsberg, Hl</t>
+          <t>Deromeskogen, Hl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>322874</v>
+        <v>322797</v>
       </c>
       <c r="R14" t="n">
-        <v>6373103</v>
+        <v>6373105</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2104,7 +2109,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt nordfladdermus. Observationen bygger på flera registreringar, artbestämningen säker.</t>
+          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33 Analysprogram: Chirpity</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,22 +2124,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Gabriel  Ulvros</t>
+          <t>Carolos Borg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Gabriel  Ulvros</t>
+          <t>Carolos Borg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127756227</v>
+        <v>127705066</v>
       </c>
       <c r="B15" t="n">
-        <v>56550</v>
+        <v>57536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,50 +2147,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205995</v>
+        <v>100096</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Oskarsberg, Hl</t>
+          <t>Deromeskogen, Hl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>322874</v>
+        <v>322797</v>
       </c>
       <c r="R15" t="n">
-        <v>6373103</v>
+        <v>6373105</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2209,17 +2209,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt dvärgpipistrell. Observationen bygger på flera registreringar, artbestämningen säker.</t>
+          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33 Analysprogram: Chirpity</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2234,12 +2234,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Gabriel  Ulvros</t>
+          <t>Carolos Borg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Gabriel  Ulvros</t>
+          <t>Carolos Borg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -1335,60 +1335,61 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127704182</v>
+        <v>127756127</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>56538</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>205992</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Deromeskogen, Hl</t>
+          <t>Oskarsberg, Hl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>322797</v>
+        <v>322874</v>
       </c>
       <c r="R8" t="n">
-        <v>6373105</v>
+        <v>6373103</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1423,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33</t>
+          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt vattenfladdermus. Observationen bygger på flera registreringar, artbestämningen säker.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,44 +1438,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Carolos Borg</t>
+          <t>Gabriel  Ulvros</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carolos Borg</t>
+          <t>Gabriel  Ulvros</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127756127</v>
+        <v>127756180</v>
       </c>
       <c r="B9" t="n">
-        <v>56538</v>
+        <v>56531</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1537,7 +1538,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt vattenfladdermus. Observationen bygger på flera registreringar, artbestämningen säker.</t>
+          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt nordfladdermus. Observationen bygger på flera registreringar, artbestämningen säker.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,32 +1565,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127756180</v>
+        <v>127756227</v>
       </c>
       <c r="B10" t="n">
-        <v>56531</v>
+        <v>56550</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1652,7 +1653,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt nordfladdermus. Observationen bygger på flera registreringar, artbestämningen säker.</t>
+          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt dvärgpipistrell. Observationen bygger på flera registreringar, artbestämningen säker.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127756227</v>
+        <v>127704348</v>
       </c>
       <c r="B11" t="n">
-        <v>56550</v>
+        <v>58140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,50 +1691,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205995</v>
+        <v>100058</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Mindre flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Ficedula parva</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Bechstein, 1794)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Oskarsberg, Hl</t>
+          <t>Deromeskogen, Hl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>322874</v>
+        <v>322797</v>
       </c>
       <c r="R11" t="n">
-        <v>6373103</v>
+        <v>6373105</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1757,17 +1757,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt dvärgpipistrell. Observationen bygger på flera registreringar, artbestämningen säker.</t>
+          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33 Analysprogram: Chirpity</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,44 +1782,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Gabriel  Ulvros</t>
+          <t>Carolos Borg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Gabriel  Ulvros</t>
+          <t>Carolos Borg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127704348</v>
+        <v>127704700</v>
       </c>
       <c r="B12" t="n">
-        <v>58140</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100058</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre flugsnappare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ficedula parva</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bechstein, 1794)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>127131832</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127131856</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>127131884</v>
       </c>
       <c r="B5" t="n">
-        <v>57821</v>
+        <v>57824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127131819</v>
       </c>
       <c r="B6" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>127131873</v>
       </c>
       <c r="B7" t="n">
-        <v>58296</v>
+        <v>58299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>127756127</v>
       </c>
       <c r="B8" t="n">
-        <v>56538</v>
+        <v>56541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>127756180</v>
       </c>
       <c r="B9" t="n">
-        <v>56531</v>
+        <v>56534</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127756227</v>
       </c>
       <c r="B10" t="n">
-        <v>56550</v>
+        <v>56553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>127704348</v>
       </c>
       <c r="B11" t="n">
-        <v>58140</v>
+        <v>58143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127704700</v>
+        <v>127704592</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>58101</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,21 +1805,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>102999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127704592</v>
+        <v>127704700</v>
       </c>
       <c r="B13" t="n">
-        <v>58098</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102999</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2025,7 +2025,7 @@
         <v>127704255</v>
       </c>
       <c r="B14" t="n">
-        <v>58093</v>
+        <v>58096</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>127705066</v>
       </c>
       <c r="B15" t="n">
-        <v>57536</v>
+        <v>57539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>127131832</v>
       </c>
       <c r="B3" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127131856</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>127131884</v>
       </c>
       <c r="B5" t="n">
-        <v>57824</v>
+        <v>57830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127131819</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>127131873</v>
       </c>
       <c r="B7" t="n">
-        <v>58299</v>
+        <v>58305</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>127756127</v>
       </c>
       <c r="B8" t="n">
-        <v>56541</v>
+        <v>56547</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>127756180</v>
       </c>
       <c r="B9" t="n">
-        <v>56534</v>
+        <v>56540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127756227</v>
       </c>
       <c r="B10" t="n">
-        <v>56553</v>
+        <v>56559</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>127704348</v>
       </c>
       <c r="B11" t="n">
-        <v>58143</v>
+        <v>58149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>127704592</v>
       </c>
       <c r="B12" t="n">
-        <v>58101</v>
+        <v>58107</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>127704700</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>127704255</v>
       </c>
       <c r="B14" t="n">
-        <v>58096</v>
+        <v>58102</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>127705066</v>
       </c>
       <c r="B15" t="n">
-        <v>57539</v>
+        <v>57545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127704592</v>
+        <v>127704700</v>
       </c>
       <c r="B12" t="n">
-        <v>58107</v>
+        <v>57832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,21 +1805,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102999</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127704700</v>
+        <v>127704592</v>
       </c>
       <c r="B13" t="n">
-        <v>57832</v>
+        <v>58107</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>102999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127704700</v>
+        <v>127704592</v>
       </c>
       <c r="B12" t="n">
-        <v>57832</v>
+        <v>58107</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,21 +1805,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>102999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127704592</v>
+        <v>127704700</v>
       </c>
       <c r="B13" t="n">
-        <v>58107</v>
+        <v>57832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102999</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -1683,7 +1683,7 @@
         <v>127704348</v>
       </c>
       <c r="B11" t="n">
-        <v>58149</v>
+        <v>58150</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127704592</v>
+        <v>127704700</v>
       </c>
       <c r="B12" t="n">
-        <v>58107</v>
+        <v>57833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,21 +1805,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102999</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127704700</v>
+        <v>127704592</v>
       </c>
       <c r="B13" t="n">
-        <v>57832</v>
+        <v>58108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>102999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2025,7 +2025,7 @@
         <v>127704255</v>
       </c>
       <c r="B14" t="n">
-        <v>58102</v>
+        <v>58103</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127704700</v>
+        <v>127704592</v>
       </c>
       <c r="B12" t="n">
-        <v>57833</v>
+        <v>58108</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,21 +1805,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>102999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127704592</v>
+        <v>127704700</v>
       </c>
       <c r="B13" t="n">
-        <v>58108</v>
+        <v>57833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102999</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -1338,7 +1338,7 @@
         <v>127756127</v>
       </c>
       <c r="B8" t="n">
-        <v>56547</v>
+        <v>56559</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>127756180</v>
       </c>
       <c r="B9" t="n">
-        <v>56540</v>
+        <v>56552</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127756227</v>
       </c>
       <c r="B10" t="n">
-        <v>56559</v>
+        <v>56571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>127704348</v>
       </c>
       <c r="B11" t="n">
-        <v>58150</v>
+        <v>58162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127704592</v>
+        <v>127704700</v>
       </c>
       <c r="B12" t="n">
-        <v>58108</v>
+        <v>57845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,21 +1805,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102999</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127704700</v>
+        <v>127704592</v>
       </c>
       <c r="B13" t="n">
-        <v>57833</v>
+        <v>58120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>102999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2025,7 +2025,7 @@
         <v>127704255</v>
       </c>
       <c r="B14" t="n">
-        <v>58103</v>
+        <v>58115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>127705066</v>
       </c>
       <c r="B15" t="n">
-        <v>57545</v>
+        <v>57557</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127704700</v>
+        <v>127704592</v>
       </c>
       <c r="B12" t="n">
-        <v>57845</v>
+        <v>58120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,21 +1805,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>102999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127704592</v>
+        <v>127704700</v>
       </c>
       <c r="B13" t="n">
-        <v>58120</v>
+        <v>57845</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102999</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>127131832</v>
       </c>
       <c r="B3" t="n">
-        <v>58042</v>
+        <v>58027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127131856</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>127131884</v>
       </c>
       <c r="B5" t="n">
-        <v>57830</v>
+        <v>57815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127131819</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>127131832</v>
       </c>
       <c r="B3" t="n">
-        <v>58027</v>
+        <v>58042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127131856</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>127131884</v>
       </c>
       <c r="B5" t="n">
-        <v>57815</v>
+        <v>57830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>127131819</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>57669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34409-2025 artfynd.xlsx
+++ b/artfynd/A 34409-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78754970</v>
+        <v>127131819</v>
       </c>
       <c r="B2" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kungsbacka, Hl</t>
+          <t>Deromeskogen, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>322740.7602495952</v>
+        <v>322797</v>
       </c>
       <c r="R2" t="n">
-        <v>6373137.806141501</v>
+        <v>6373105</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,27 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Mycket gott om murgröna som klättrar på minst 8 träd</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,22 +772,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Morgan Johansson</t>
+          <t>Carolos Borg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Morgan Johansson</t>
+          <t>Carolos Borg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127131832</v>
+        <v>127705066</v>
       </c>
       <c r="B3" t="n">
-        <v>58042</v>
+        <v>57825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,16 +795,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100096</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,19 +812,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Deromeskogen, Hl</t>
@@ -871,12 +857,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33 Analysprogram: Chirpity</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +897,7 @@
         <v>127131856</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127131884</v>
+        <v>127704592</v>
       </c>
       <c r="B5" t="n">
-        <v>57830</v>
+        <v>58393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,28 +1014,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>102999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
@@ -1052,7 +1039,11 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Deromeskogen, Hl</t>
@@ -1089,12 +1080,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33 Analysprogram: Chirpity</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127131819</v>
+        <v>127704255</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>58388</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,28 +1128,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
@@ -1161,7 +1153,11 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Deromeskogen, Hl</t>
@@ -1198,12 +1194,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33 Analysprogram: Chirpity</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,27 +1231,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127131873</v>
+        <v>127131832</v>
       </c>
       <c r="B7" t="n">
-        <v>58305</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102125</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1258,7 +1259,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
@@ -1335,61 +1340,60 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127756127</v>
+        <v>127131884</v>
       </c>
       <c r="B8" t="n">
-        <v>56559</v>
+        <v>58112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205992</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Oskarsberg, Hl</t>
+          <t>Deromeskogen, Hl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>322874</v>
+        <v>322797</v>
       </c>
       <c r="R8" t="n">
-        <v>6373103</v>
+        <v>6373105</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,17 +1417,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt vattenfladdermus. Observationen bygger på flera registreringar, artbestämningen säker.</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,22 +1437,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gabriel  Ulvros</t>
+          <t>Carolos Borg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gabriel  Ulvros</t>
+          <t>Carolos Borg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127756180</v>
+        <v>127704182</v>
       </c>
       <c r="B9" t="n">
-        <v>56552</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,50 +1460,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205998</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Oskarsberg, Hl</t>
+          <t>Deromeskogen, Hl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>322874</v>
+        <v>322797</v>
       </c>
       <c r="R9" t="n">
-        <v>6373103</v>
+        <v>6373105</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,7 +1536,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt nordfladdermus. Observationen bygger på flera registreringar, artbestämningen säker.</t>
+          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33 Analysprogram: Chirpity</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,22 +1551,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Gabriel  Ulvros</t>
+          <t>Carolos Borg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gabriel  Ulvros</t>
+          <t>Carolos Borg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127756227</v>
+        <v>127756127</v>
       </c>
       <c r="B10" t="n">
-        <v>56571</v>
+        <v>56823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,21 +1574,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1653,7 +1651,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt dvärgpipistrell. Observationen bygger på flera registreringar, artbestämningen säker.</t>
+          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt vattenfladdermus. Observationen bygger på flera registreringar, artbestämningen säker.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127704348</v>
+        <v>127756227</v>
       </c>
       <c r="B11" t="n">
-        <v>58162</v>
+        <v>56835</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,49 +1689,50 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100058</v>
+        <v>205995</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre flugsnappare</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula parva</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1794)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Deromeskogen, Hl</t>
+          <t>Oskarsberg, Hl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>322797</v>
+        <v>322874</v>
       </c>
       <c r="R11" t="n">
-        <v>6373105</v>
+        <v>6373103</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1757,17 +1756,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33 Analysprogram: Chirpity</t>
+          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt dvärgpipistrell. Observationen bygger på flera registreringar, artbestämningen säker.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,22 +1781,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Carolos Borg</t>
+          <t>Gabriel  Ulvros</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carolos Borg</t>
+          <t>Gabriel  Ulvros</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127704592</v>
+        <v>127756180</v>
       </c>
       <c r="B12" t="n">
-        <v>58120</v>
+        <v>56816</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,49 +1804,50 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102999</v>
+        <v>205998</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Deromeskogen, Hl</t>
+          <t>Oskarsberg, Hl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>322797</v>
+        <v>322874</v>
       </c>
       <c r="R12" t="n">
-        <v>6373105</v>
+        <v>6373103</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1871,17 +1871,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33 Analysprogram: Chirpity</t>
+          <t>Flera inspelningar med Audiomoth under kvällen. Analysen visar tydligt nordfladdermus. Observationen bygger på flera registreringar, artbestämningen säker.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,72 +1896,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Carolos Borg</t>
+          <t>Gabriel  Ulvros</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carolos Borg</t>
+          <t>Gabriel  Ulvros</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127704700</v>
+        <v>78754970</v>
       </c>
       <c r="B13" t="n">
-        <v>57845</v>
+        <v>111176</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>219677</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Deromeskogen, Hl</t>
+          <t>Kungsbacka, Hl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>322797</v>
+        <v>322741</v>
       </c>
       <c r="R13" t="n">
-        <v>6373105</v>
+        <v>6373138</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1985,17 +1975,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2019-07-05</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2019-07-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33 Analysprogram: Chirpity</t>
+          <t>Mycket gott om murgröna som klättrar på minst 8 träd</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,239 +2010,15 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carolos Borg</t>
+          <t>Morgan Johansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carolos Borg</t>
+          <t>Morgan Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>127704255</v>
-      </c>
-      <c r="B14" t="n">
-        <v>58115</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>103001</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Rödvingetrast</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Turdus iliacus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Deromeskogen, Hl</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>322797</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6373105</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Halland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Kungsbacka</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Halland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Vallda</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33 Analysprogram: Chirpity</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Carolos Borg</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Carolos Borg</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>127705066</v>
-      </c>
-      <c r="B15" t="n">
-        <v>57557</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>100096</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Pandion haliaetus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Deromeskogen, Hl</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>322797</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6373105</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Halland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Kungsbacka</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Halland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Vallda</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Audiomoth ljudbox 11-12 aug östra delen av Deromeskogen Minimum confidence: 0,8 Sensitivy:1 Species by location Lat 57 Long 12 Week:33 Analysprogram: Chirpity</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Carolos Borg</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Carolos Borg</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
